--- a/Compititor's_Price/Cladco_Prices/Cladco_Prices_03-12-2025.xlsx
+++ b/Compititor's_Price/Cladco_Prices/Cladco_Prices_03-12-2025.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Kellaway Building Supplies</t>
+          <t>Kellaway</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-hollow-grooved-composite-decking-board-in-charcoal</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +524,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -535,7 +561,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -572,7 +598,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -594,7 +620,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/22-hollow-domestic-grade</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -609,7 +661,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -646,7 +698,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -683,7 +735,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -720,7 +772,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -757,7 +809,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -779,7 +831,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -794,7 +872,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -816,7 +894,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -831,7 +935,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -853,7 +957,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -868,7 +998,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -890,7 +1020,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -905,7 +1061,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -927,7 +1083,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -942,7 +1124,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -964,7 +1146,33 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -979,7 +1187,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1209,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1016,7 +1250,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1272,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1053,7 +1313,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1335,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1090,7 +1376,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1398,33 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1127,7 +1439,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1461,33 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1164,7 +1502,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1524,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1201,7 +1565,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1587,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1238,7 +1628,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1650,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1275,7 +1691,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1713,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1312,7 +1754,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1776,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1349,7 +1817,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1839,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1386,7 +1880,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1902,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1423,7 +1943,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1965,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1460,7 +2006,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1482,7 +2028,33 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1497,7 +2069,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1519,22 +2091,48 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.tradingdepot.co.uk/wpcsc40-cladco-wpc-solid-composite-decking-board</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradingdepot.co.uk', port=443): Read timed out. (read timeout=None)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>£27.58</t>
+          <t>Error: HTTPSConnectionPool(host='www.roofingoutlet.co.uk', port=443): Max retries exceeded with url: /products/cladco-solid-commercial-grade-composite-decking-board-teak-4m (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A092850&gt;: Failed to resolve 'www.roofingoutlet.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1551,27 +2149,60 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/cladco-composite-decking-board-solid-150mm-x-25mm-x-4m-all-colours?variant=41749854322881 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000014C860F4050&gt;: Failed to establish a new connection: [WinError 10053] An established connection was aborted by the software in your host machine'))</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=142.0.7444.176)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8abc77
+	0x89eec8
+	0x8a0884
+	0x89f396
+	0x89ec82
+	0x89e98d
+	0x89c7fe
+	0x89d28b
+	0x8b24ce
+	0x93fb37
+	0x91c90c
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.tradingdepot.co.uk/wpcsr40-cladco-wpc-solid-composite-decking-board</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradingdepot.co.uk', port=443): Max retries exceeded with url: /wpcsr40-cladco-wpc-solid-composite-decking-board (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A092850&gt;: Failed to resolve 'www.tradingdepot.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>£27.58</t>
+          <t>Error: HTTPSConnectionPool(host='www.roofingoutlet.co.uk', port=443): Max retries exceeded with url: /products/cladco-solid-commercial-grade-composite-decking-board-redwood-4m (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A092710&gt;: Failed to resolve 'www.roofingoutlet.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1588,27 +2219,60 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/cladco-composite-decking-board-solid-150mm-x-25mm-x-4m-all-colours?variant=41749854355649 (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A0916D0&gt;: Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=142.0.7444.176)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8abc77
+	0x89eec8
+	0x8a0884
+	0x89f396
+	0x89ec82
+	0x89e98d
+	0x89c7fe
+	0x89d28b
+	0x8b24ce
+	0x93fb37
+	0x91c90c
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.tradingdepot.co.uk/wpcso40-cladco-wpc-solid-composite-decking-board</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradingdepot.co.uk', port=443): Max retries exceeded with url: /wpcso40-cladco-wpc-solid-composite-decking-board (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A092FD0&gt;: Failed to resolve 'www.tradingdepot.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>£27.58</t>
+          <t>Error: HTTPSConnectionPool(host='www.roofingoutlet.co.uk', port=443): Max retries exceeded with url: /products/cladco-solid-commercial-grade-composite-decking-board-olive-green-4m (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A093110&gt;: Failed to resolve 'www.roofingoutlet.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1625,27 +2289,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/cladco-composite-decking-board-solid-150mm-x-25mm-x-4m-all-colours?variant=41749854388417 (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A092D50&gt;: Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=142.0.7444.176)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8abc77
+	0x89eec8
+	0x8a0884
+	0x89f396
+	0x89ec82
+	0x89e98d
+	0x89c7fe
+	0x89d28b
+	0x8b24ce
+	0x93fb37
+	0x91c90c
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.tradingdepot.co.uk/wpcsi40-cladco-wpc-solid-composite-decking-board</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradingdepot.co.uk', port=443): Max retries exceeded with url: /wpcsi40-cladco-wpc-solid-composite-decking-board (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A093250&gt;: Failed to resolve 'www.tradingdepot.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>£27.58</t>
+          <t>Error: HTTPSConnectionPool(host='www.roofingoutlet.co.uk', port=443): Max retries exceeded with url: /products/cladco-solid-commercial-grade-composite-decking-board-ivory-4m (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A093750&gt;: Failed to resolve 'www.roofingoutlet.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1662,7 +2359,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>£36.00</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/cladco-composite-bullnose-decking-board-150mm-x-25mm-x-4m-all-colours?_pos=1&amp;_sid=a66bb941b&amp;_ss=r&amp;variant=41758908645569 (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A093B10&gt;: Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1672,17 +2369,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.tradingdepot.co.uk/wpcsb40b-cladco-wpc-bullnose-composite-decking-board</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradingdepot.co.uk', port=443): Max retries exceeded with url: /wpcsb40b-cladco-wpc-bullnose-composite-decking-board (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C8A093ED0&gt;: Failed to resolve 'www.tradingdepot.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>£35.38</t>
+          <t>Error: HTTPSConnectionPool(host='www.roofingoutlet.co.uk', port=443): Max retries exceeded with url: /products/cladco-solid-bullnose-commercial-grade-composite-decking-board-4m-all-colours?variant=40044402049095 (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x0000014C866F4190&gt;: Failed to resolve 'www.roofingoutlet.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1704,7 +2401,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-bullnose-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1719,7 +2442,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1756,7 +2479,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1793,7 +2516,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1815,7 +2538,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-bullnose-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1830,7 +2579,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1852,7 +2601,33 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-bullnose-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1867,7 +2642,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1904,7 +2679,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1941,7 +2716,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -1958,7 +2733,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1978,7 +2753,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2775,33 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2015,7 +2816,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2838,33 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2052,7 +2879,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2901,33 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2089,7 +2942,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2964,33 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2126,7 +3005,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2148,7 +3027,33 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2163,7 +3068,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2185,7 +3090,33 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2200,7 +3131,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2222,7 +3153,33 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2237,7 +3194,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2259,7 +3216,33 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2274,7 +3257,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2296,7 +3279,33 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2311,7 +3320,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2333,7 +3342,33 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2348,7 +3383,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2370,7 +3405,33 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2385,7 +3446,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2407,7 +3468,33 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2422,7 +3509,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2444,7 +3531,33 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2459,7 +3572,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2481,7 +3594,33 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2496,7 +3635,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2518,7 +3657,33 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2533,7 +3698,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2555,7 +3720,33 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2570,7 +3761,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2592,7 +3783,33 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2607,7 +3824,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2629,7 +3846,33 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2644,7 +3887,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2666,7 +3909,33 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2681,7 +3950,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2703,7 +3972,33 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2718,7 +4013,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2740,7 +4035,33 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2755,7 +4076,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2777,7 +4098,33 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2792,7 +4139,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2814,7 +4161,33 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2829,7 +4202,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2851,7 +4224,33 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2866,7 +4265,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2888,7 +4287,33 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2903,7 +4328,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2925,7 +4350,33 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2940,7 +4391,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2962,7 +4413,33 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2977,7 +4454,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -2999,7 +4476,33 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3014,7 +4517,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3036,7 +4539,33 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3051,7 +4580,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3073,7 +4602,33 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3088,7 +4643,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3110,7 +4665,33 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3125,7 +4706,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3147,7 +4728,33 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3162,7 +4769,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3184,7 +4791,33 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3199,7 +4832,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3221,7 +4854,33 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3236,7 +4895,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3258,7 +4917,33 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-joists-batten</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3273,7 +4958,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3295,7 +4980,33 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/structural-composite-joist</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3310,7 +5021,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3332,7 +5043,33 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-starter-clips-pack-of-50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3347,7 +5084,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3369,7 +5106,33 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-t-clip-fixings-and-screws</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3406,7 +5169,33 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-stainless-clips</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3421,7 +5210,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3443,7 +5232,33 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/m4-40mm-stainless-steel-fibre-cement</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3458,7 +5273,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3480,7 +5295,33 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-heavy-duty-weed-control-mat</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3495,7 +5336,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3517,7 +5358,33 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-weed-mat-pins</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3532,7 +5399,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3554,7 +5421,33 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/owatrol-composite-decking-cleaner</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3569,7 +5462,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3586,12 +5479,38 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/owatrol-compo-care-composite-decking-reviver</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3606,7 +5525,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3623,12 +5542,38 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/owatrol-compo-care-composite-decking-reviver</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3643,7 +5588,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3660,7 +5605,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3680,7 +5625,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3702,7 +5647,33 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/universal-sealant-gun-310ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3717,7 +5688,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -3739,7 +5710,33 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3776,7 +5773,33 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3813,7 +5836,33 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3850,7 +5899,33 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3887,7 +5962,33 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3924,7 +6025,33 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3961,7 +6088,33 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3998,7 +6151,33 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4035,7 +6214,33 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4072,7 +6277,33 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4109,7 +6340,33 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4146,7 +6403,33 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4183,7 +6466,33 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4220,7 +6529,33 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4257,7 +6592,33 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4294,7 +6655,33 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4331,7 +6718,33 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding-starter-strip</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4346,7 +6759,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4368,7 +6781,33 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4383,7 +6822,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4405,7 +6844,33 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4420,7 +6885,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4442,7 +6907,33 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4457,7 +6948,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4479,7 +6970,33 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4494,7 +7011,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4516,7 +7033,33 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4531,7 +7074,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4553,7 +7096,33 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4568,7 +7137,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4590,7 +7159,33 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4605,7 +7200,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4627,7 +7222,33 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4642,7 +7263,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4664,7 +7285,33 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4679,7 +7326,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4701,7 +7348,33 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4716,7 +7389,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4738,7 +7411,33 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4753,7 +7452,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4775,7 +7474,33 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4790,7 +7515,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4812,7 +7537,33 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4827,7 +7578,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4849,7 +7600,33 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4864,7 +7641,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4886,7 +7663,33 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4901,7 +7704,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4923,7 +7726,33 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4938,7 +7767,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4960,7 +7789,33 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4975,7 +7830,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -4997,7 +7852,33 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5012,7 +7893,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5029,12 +7910,38 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5049,7 +7956,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5071,7 +7978,33 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5086,7 +8019,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5108,7 +8041,33 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5123,7 +8082,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5145,7 +8104,33 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5160,7 +8145,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5182,7 +8167,33 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5197,7 +8208,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5219,7 +8230,33 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5234,7 +8271,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5256,7 +8293,33 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5271,7 +8334,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5293,7 +8356,33 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5308,7 +8397,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5330,7 +8419,33 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5345,7 +8460,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5367,7 +8482,33 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5382,7 +8523,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5404,7 +8545,33 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5419,7 +8586,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5441,7 +8608,33 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5456,7 +8649,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5478,7 +8671,33 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5493,7 +8712,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5515,7 +8734,33 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5530,7 +8775,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5552,7 +8797,33 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5567,7 +8838,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5589,7 +8860,33 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5604,7 +8901,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5626,7 +8923,33 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5641,7 +8964,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5663,7 +8986,33 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5678,7 +9027,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5700,7 +9049,33 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5715,7 +9090,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5737,7 +9112,33 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5752,7 +9153,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5774,7 +9175,33 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5789,7 +9216,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5806,12 +9233,38 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>N/L or Discontinued</t>
+          <t>N/L</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5826,7 +9279,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5848,7 +9301,33 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3m-aluminium-perforated-closure</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5863,7 +9342,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5885,7 +9364,33 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5900,7 +9405,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5922,7 +9427,33 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5937,7 +9468,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5959,7 +9490,33 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5974,7 +9531,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -5996,7 +9553,33 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6011,7 +9594,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6033,7 +9616,33 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6048,7 +9657,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6070,7 +9679,33 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6085,7 +9720,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6107,7 +9742,33 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6122,7 +9783,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6144,7 +9805,33 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6159,7 +9846,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6181,7 +9868,33 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6196,7 +9909,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6218,7 +9931,33 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6233,7 +9972,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6255,7 +9994,33 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6270,7 +10035,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6292,7 +10057,33 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6307,7 +10098,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6329,7 +10120,33 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6344,7 +10161,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6366,7 +10183,33 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6381,7 +10224,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6403,7 +10246,33 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6418,7 +10287,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6440,7 +10309,33 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6455,7 +10350,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6477,7 +10372,33 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6492,7 +10413,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6514,7 +10435,33 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6529,7 +10476,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6551,7 +10498,33 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6566,7 +10539,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6588,7 +10561,33 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6603,7 +10602,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6625,7 +10624,33 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6640,7 +10665,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6662,7 +10687,33 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6677,7 +10728,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6699,7 +10750,33 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6714,7 +10791,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6736,7 +10813,33 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6751,7 +10854,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6773,7 +10876,33 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6788,7 +10917,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6805,12 +10934,38 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>£26.27</t>
+          <t>Error: 502 Server Error: Bad Gateway for url: https://build4less.co.uk/products/cladco-fibre-cement-wall-caldding-internal-corner-profile-trim-x-3m-all-colours?variant=41766456262849</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6825,7 +10980,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6847,7 +11002,33 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6862,7 +11043,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6884,7 +11065,33 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6899,7 +11106,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6921,7 +11128,33 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6936,7 +11169,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6958,7 +11191,33 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6973,7 +11232,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -6995,7 +11254,33 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7010,7 +11295,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7032,7 +11317,33 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7047,7 +11358,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7069,7 +11380,33 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7084,7 +11421,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7106,7 +11443,33 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7121,7 +11484,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7143,7 +11506,33 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7158,7 +11547,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7180,7 +11569,33 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -7195,7 +11610,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7217,7 +11632,33 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7232,7 +11673,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7254,7 +11695,33 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7269,7 +11736,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7291,7 +11758,33 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7306,7 +11799,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7328,7 +11821,33 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -7343,7 +11862,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7365,7 +11884,33 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7380,7 +11925,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7402,7 +11947,33 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7417,7 +11988,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7439,7 +12010,33 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7454,7 +12051,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7476,7 +12073,33 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7491,7 +12114,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7513,7 +12136,33 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7528,7 +12177,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7550,7 +12199,33 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7565,7 +12240,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7587,7 +12262,33 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7602,7 +12303,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7624,7 +12325,33 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7639,7 +12366,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7661,7 +12388,33 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7676,7 +12429,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7698,7 +12451,33 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7713,7 +12492,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7735,7 +12514,33 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7750,7 +12555,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7772,7 +12577,33 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7787,7 +12618,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7809,7 +12640,33 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7824,7 +12681,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7846,7 +12703,33 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7861,7 +12744,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7883,7 +12766,33 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7898,7 +12807,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7920,7 +12829,33 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -7935,7 +12870,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7957,7 +12892,33 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7972,7 +12933,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -7994,7 +12955,33 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -8009,7 +12996,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8031,7 +13018,33 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -8046,7 +13059,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8068,7 +13081,33 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -8083,7 +13122,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8105,7 +13144,33 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -8120,7 +13185,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8142,7 +13207,33 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -8157,7 +13248,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8179,7 +13270,33 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -8194,7 +13311,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8216,7 +13333,33 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -8231,7 +13374,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8253,7 +13396,33 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -8268,7 +13437,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8290,7 +13459,33 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -8305,7 +13500,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8327,7 +13522,33 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -8342,7 +13563,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8364,7 +13585,33 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -8379,7 +13626,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8401,7 +13648,33 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-black-balustrade-handrail-post</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -8416,7 +13689,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8438,7 +13711,33 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/balustrade-handrail-gate-aluminium-powder-coated-material</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8453,7 +13752,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8490,7 +13789,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8527,7 +13826,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8564,7 +13863,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8586,7 +13885,33 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/recycled-plastic-cladding-batten-50mm-x-50mm-x-3m-length-black</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -8601,7 +13926,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8623,7 +13948,33 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-recycled-plastic-post-100x100</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -8638,7 +13989,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8660,7 +14011,33 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/recycled-plastic-joist-50mm-x-100mm-x-3-6m-length-black</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8675,7 +14052,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8697,7 +14074,33 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-recycled-plastic-joist-50x150-3m-black</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -8712,7 +14115,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8734,7 +14137,33 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/frame-protection-deck-tape-65mm-x-20m-roll-black</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8749,7 +14178,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8771,7 +14200,33 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -8786,7 +14241,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8808,7 +14263,33 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -8823,7 +14304,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8845,7 +14326,33 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -8860,7 +14367,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8882,7 +14389,33 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -8897,7 +14430,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8919,7 +14452,33 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -8934,7 +14493,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8956,7 +14515,33 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -8971,7 +14556,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -8993,7 +14578,33 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -9008,7 +14619,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9030,7 +14641,33 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -9045,7 +14682,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9067,7 +14704,33 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -9082,7 +14745,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9104,7 +14767,33 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -9119,7 +14808,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9141,7 +14830,33 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -9156,7 +14871,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
@@ -9178,7 +14893,33 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xaa4103
+	0xaa4144
+	0x8ae71d
+	0x8fa03d
+	0x8fa41b
+	0x9417f2
+	0x91c954
+	0x93ee17
+	0x91c706
+	0x8eda30
+	0x8eed54
+	0xd157b4
+	0xd1098a
+	0xacc392
+	0xabc4c8
+	0xac324d
+	0xaac478
+	0xaac63c
+	0xa967ca
+	0x77015d49
+	0x77d0d6db
+	0x77d0d661
+</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -9193,7 +14934,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>N\L</t>
+          <t>N/L</t>
         </is>
       </c>
     </row>
